--- a/outputs/self_refine_top2_lora/04_para_rubrica_self_refine_top2_lora.xlsx
+++ b/outputs/self_refine_top2_lora/04_para_rubrica_self_refine_top2_lora.xlsx
@@ -505,7 +505,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>No tiene motivación ni incentivos, dos cosas clave para competir.</t>
+          <t>No tiene motivación ni incentivos, dos elementos clave en ambientes competitivos.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -541,7 +541,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -560,7 +560,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>En los procesos de importaciones y exportaciones intervienen clientes y proveedores, así como instituciones del Estado y bancos.</t>
+          <t>En los procesos de importaciones y exportaciones intervienen clientes, proveedores, instituciones del Estado y bancos, como se indica en el siguiente recuadro.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -577,7 +577,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -632,7 +632,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Los sueños de los niños tienen una gran variedad. Algunos son Tarzán, Superman o el Agente 007.</t>
+          <t>Los sueños de los niños son muy variados, desde Tarzán hasta Superman.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -649,7 +649,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -668,7 +668,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Expresiones como soborno y cohecho son ilícitos que involucran comprar la voluntad de alguien para beneficio personal.</t>
+          <t>Expresiones como soborno y cohecho se refieren a actos ilícitos que involucran comprar la voluntad de alguien para beneficio personal.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -685,7 +685,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -740,7 +740,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El interés compuesto es la suma del capital y el interés acumulado. Se multiplica según los plazos convenidos. La tasa de interés es el porcentaje que se aplica a un préstamo o inversión.</t>
+          <t>El interés compuesto es la suma del capital y el interés acumulado. La tasa de interés es el porcentaje que se aplica a un préstamo o inversión.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -757,7 +757,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>La producción en un país se hace con los factores de producción.</t>
+          <t>La producción en un país se hace con los factores de producción. Se hablará más sobre ellos después.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -793,7 +793,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>A pesar de las críticas, el intermediario es necesario en la economía.</t>
+          <t>Algunos critican al intermediario, pero es necesario para la economía.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -829,7 +829,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>46</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -884,7 +884,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>También es útil separar las metas en tres períodos de tiempo para planificar. Aunque se ha abordado esto antes, es importante recordarlo para gestionar mejor el tema presente.</t>
+          <t>Separe las metas en tres períodos de tiempo para planificar. Aunque se ha hablado sobre esto antes, es importante recordarlo para manejar mejor el tema actual.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -901,7 +901,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>La seguridad financiera es cumplir con las necesidades futuras de las personas y pagar las cuentas diarias.</t>
+          <t>La seguridad financiera consiste en cubrir las necesidades futuras de las personas y pagar las cuentas diarias.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -937,7 +937,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -956,7 +956,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>La última razón es encontrar un campo intelectual interesante para comprender el mundo real.</t>
+          <t>La última razón puede ser encontrar un campo fascinante para comprender el mundo real.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -973,7 +973,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Si el entusiasmo se orienta hacia la salud, belleza, éxito y felicidad, es probable obtener estos resultados.</t>
+          <t>Si el entusiasmo se orienta hacia la salud, belleza y éxito, se obtendrá justamente eso.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1009,7 +1009,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>En la segunda etapa de programación se definen los objetivos y metas claros para saber qué se quiere lograr con las inversiones. Por ejemplo, se establecen tipos de inversión y montos a alcanzar en un plazo determinado.</t>
+          <t>En la segunda etapa de programación se definen los objetivos y se establecen metas claras y precisas para saber qué se quiere lograr con las inversiones. Por ejemplo, se determinan los tipos de inversión y los montos que se desean alcanzar en un plazo definido.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1045,7 +1045,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1117,7 +1117,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Existen varias modalidades de cheques, como mencionan Alonso, Brailovsky y Ortiz.</t>
+          <t>Existen varias modalidades de cheques.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1153,7 +1153,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>La mayor ventaja es la flexibilidad para pagar saldos, ya sea al completo cada mes o en parte.</t>
+          <t>La mayor ventaja es la flexibilidad que le da al usuario. Puede pagar sus saldos por completo cada mes o pagar parte de ellos.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1189,7 +1189,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>El dinero que inviertes al principio se llama capital.</t>
+          <t>El dinero que se invierte al principio se llama capital.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1225,7 +1225,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>57</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Existen modelos para determinar la tasa de descuento. Sin embargo, estos modelos no se incluyen aquí. En su lugar, la tasa de descuento exigida por el accionista puede ser estimada subjetivamente.</t>
+          <t>Existen modelos cuantitativos que permiten determinar la tasa de descuento. Sin embargo, si no se dispone de esa información, se puede utilizar una estimación subjetiva para determinar la tasa de descuento exigida por el accionista.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1261,7 +1261,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Obtenga el rendimiento de un bono de diez mil dólares que paga el 6%.</t>
+          <t>Obtenga el rendimiento de un bono de diez mil dólares que paga el seis por ciento.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>24</v>
+        <v>60</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>El tema concierne a todos los individuos y durante toda la vida, ya que las finanzas explican cómo se obtienen y se utilizan los ingresos para satisfacer nuestras necesidades personales.</t>
+          <t>El tema de las finanzas concierne a todos los individuos y durante toda la vida. Las finanzas explican cómo se obtienen y se utilizan los ingresos para satisfacer las necesidades personales.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1369,7 +1369,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Estos principios fomentan la educación de los ciudadanos sobre servicios financieros.</t>
+          <t>Estos principios promueven la educación de los ciudadanos sobre servicios financieros.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -1441,7 +1441,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hable con ellos, déles la cara y explíqueles que está haciendo todo lo posible para pagarles.</t>
+          <t>Comuníquese con ellos y hágales saber que está haciendo todo lo posible para pagarles.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -1477,7 +1477,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Pero ¿qué se compite?</t>
+          <t>¿En qué se compete?</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Algunas personas creen que un impuesto del 10% impondría el mismo sacrificio a ambas familias.</t>
+          <t>Algunas personas creen que un impuesto del 10% sería igual de duro para ambas familias.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -1549,7 +1549,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Al principio, se convirtió en mercancía, pero con el tiempo pasó a ser dinero-papel, cuentas corrientes y otras formas.</t>
+          <t>Al principio, adoptó la forma de mercancía. Luego se convirtió en dinero-papel, cuentas corrientes y otras formas.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -1585,7 +1585,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>¿Son solo sueños o metas reales?</t>
+          <t>¿Son estos sueños reales?</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -1621,7 +1621,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>En los pueblos donde todos pueden elegir, no hay carrera pública.</t>
+          <t>En los pueblos donde todos pueden elegir, no hay una carrera pública como tal.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -1657,7 +1657,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nunca se ha logrado algo grande sin entusiasmo.</t>
+          <t>Sin entusiasmo, nunca se logra hacer algo grande.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -1693,7 +1693,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Este método calcula intereses sobre intereses.</t>
+          <t>Este método calcula interés sobre intereses.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1729,7 +1729,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>El resultado es aproximadamente de $300,000 en seis años.</t>
+          <t>El resultado es aproximadamente trescientos mil dólares en seis años.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -1765,7 +1765,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>1</v>
       </c>
       <c r="B38" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>En los procesos de importaciones y exportaciones intervienen clientes, proveedores, instituciones del Estado y bancos, como se indica en el siguiente recuadro.</t>
+          <t>En los procesos de importaciones y exportaciones intervienen clientes y proveedores, así como instituciones del Estado y bancos.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1873,7 +1873,7 @@
         <v>3</v>
       </c>
       <c r="B40" t="n">
-        <v>39</v>
+        <v>3</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>4</v>
       </c>
       <c r="B41" t="n">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Los sueños de los niños son muy variados, desde Tarzán hasta Superman.</t>
+          <t>Los sueños de los niños tienen una gran variedad. Algunos son Tarzán, Superman o el Agente 007.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -1945,7 +1945,7 @@
         <v>5</v>
       </c>
       <c r="B42" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Expresiones como soborno y cohecho se refieren a actos ilícitos que involucran comprar la voluntad de alguien para beneficio personal.</t>
+          <t>Expresiones como soborno y cohecho son ilícitos que involucran comprar la voluntad de alguien para beneficio personal.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="B43" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>7</v>
       </c>
       <c r="B44" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>El interés compuesto es la suma del capital y el interés acumulado. La tasa de interés es el porcentaje que se aplica a un préstamo o inversión.</t>
+          <t>El interés compuesto es la suma del capital y el interés acumulado. Se multiplica según los plazos convenidos. La tasa de interés es el porcentaje que se aplica a un préstamo o inversión.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2053,7 +2053,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>La producción en un país se hace con los factores de producción. Se hablará más sobre ellos después.</t>
+          <t>La producción en un país se hace con los factores de producción.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2089,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="B46" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Algunos critican al intermediario, pero es necesario para la economía.</t>
+          <t>A pesar de las críticas, el intermediario es necesario en la economía.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -2125,7 +2125,7 @@
         <v>10</v>
       </c>
       <c r="B47" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
         <v>11</v>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Separe las metas en tres períodos de tiempo para planificar. Aunque esto se mencionó antes, es importante recordarlo para manejar mejor el tema actual.</t>
+          <t>También es útil separar las metas en tres períodos de tiempo para planificar. Aunque se ha hablado sobre esto antes, es importante recordarlo para gestionar mejor el tema actual.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -2197,7 +2197,7 @@
         <v>12</v>
       </c>
       <c r="B49" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>13</v>
       </c>
       <c r="B50" t="n">
-        <v>49</v>
+        <v>13</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>La última razón puede ser encontrar un campo fascinante para comprender el mundo real.</t>
+          <t>La última razón es encontrar un campo intelectual interesante para comprender el mundo real.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2269,7 +2269,7 @@
         <v>14</v>
       </c>
       <c r="B51" t="n">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Si el entusiasmo se orienta hacia la salud, belleza y éxito, se obtendrá justamente eso.</t>
+          <t>Si el entusiasmo se orienta hacia la salud, belleza, éxito y felicidad, es probable obtener estos resultados.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2305,7 +2305,7 @@
         <v>15</v>
       </c>
       <c r="B52" t="n">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>En la segunda etapa de programación se definen los objetivos y se establecen metas claras y precisas para saber qué se quiere lograr con las inversiones. Por ejemplo, se determinan los tipos de inversión y los montos que se desean alcanzar en un plazo definido.</t>
+          <t>En la segunda etapa de programación se definen los objetivos y metas claras para saber qué se quiere lograr con las inversiones. Por ejemplo, se establecen tipos de inversión y montos a alcanzar en un plazo determinado.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2341,7 +2341,7 @@
         <v>16</v>
       </c>
       <c r="B53" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
         <v>17</v>
       </c>
       <c r="B54" t="n">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Además, el canal móvil es ideal para realizar pagos electrónicos a través de SMS desde cualquier lugar con acceso a internet.</t>
+          <t>Además, el canal móvil es ideal para realizar pagos electrónicos a través de SMS desde cualquier lugar con conexión inalámbrica.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -2413,7 +2413,7 @@
         <v>18</v>
       </c>
       <c r="B55" t="n">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Existen varias modalidades de cheques.</t>
+          <t>Existen varias modalidades de cheques, como mencionan Alonso, Brailovsky y Ortiz.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr"/>
@@ -2449,7 +2449,7 @@
         <v>19</v>
       </c>
       <c r="B56" t="n">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>La mayor ventaja es la flexibilidad que le da al usuario. Puede pagar sus saldos por completo cada mes o pagar parte del monto.</t>
+          <t>La mayor ventaja es la flexibilidad, que permite al usuario pagar sus saldos completamente cada mes o en parte.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr"/>
@@ -2485,7 +2485,7 @@
         <v>20</v>
       </c>
       <c r="B57" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>El dinero inicialmente invertido se llama capital.</t>
+          <t>El dinero que inviertes al principio se llama capital.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
@@ -2521,7 +2521,7 @@
         <v>21</v>
       </c>
       <c r="B58" t="n">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Existen modelos cuantitativos que permiten determinar el valor de la tasa de descuento. Sin embargo, si no se dispone de esa información, se puede utilizar una estimación subjetiva para determinar la tasa de descuento exigida por el accionista.</t>
+          <t>Existen modelos para determinar la tasa de descuento. Sin embargo, estos modelos no se incluyen aquí. En su lugar, la tasa de descuento exigida por el accionista puede ser estimada subjetivamente.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr"/>
@@ -2557,7 +2557,7 @@
         <v>22</v>
       </c>
       <c r="B59" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2593,7 +2593,7 @@
         <v>23</v>
       </c>
       <c r="B60" t="n">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2629,7 +2629,7 @@
         <v>24</v>
       </c>
       <c r="B61" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>El tema de las finanzas concierne a todos los individuos y durante toda la vida. Las finanzas explican cómo se obtienen y se utilizan los ingresos para satisfacer las necesidades personales.</t>
+          <t>El tema concierne a todos los individuos y durante toda la vida, ya que las finanzas explican cómo se obtienen y se utilizan los ingresos para satisfacer nuestras necesidades personales.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="n">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>26</v>
       </c>
       <c r="B63" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Estos principios promueven la educación de los ciudadanos sobre servicios financieros.</t>
+          <t>Estos principios fomentan la educación de los ciudadanos sobre servicios financieros.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr"/>
@@ -2737,7 +2737,7 @@
         <v>27</v>
       </c>
       <c r="B64" t="n">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Comuníquese con ellos, déles la cara y hágales saber que está haciendo todo lo posible para pagarles.</t>
+          <t>Hable con ellos, déles la cara y explíqueles que está haciendo todo lo posible para pagarles.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr"/>
@@ -2773,7 +2773,7 @@
         <v>28</v>
       </c>
       <c r="B65" t="n">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>¿En qué se compete?</t>
+          <t>Pero ¿qué se compite?</t>
         </is>
       </c>
       <c r="G65" t="inlineStr"/>
@@ -2809,7 +2809,7 @@
         <v>29</v>
       </c>
       <c r="B66" t="n">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Algunas personas creen que un impuesto del 10% sería igual de duro para ambas familias.</t>
+          <t>Algunas personas creen que un impuesto del 10% impondría el mismo sacrificio a ambas familias.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr"/>
@@ -2845,7 +2845,7 @@
         <v>30</v>
       </c>
       <c r="B67" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Al principio, adoptó la forma de mercancía. Luego se convirtió en dinero-papel, cuentas corrientes y otras formas.</t>
+          <t>Al principio se convirtió en mercancía, pero con el tiempo pasó a ser dinero-papel, cuentas corrientes y otras formas.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr"/>
@@ -2881,7 +2881,7 @@
         <v>31</v>
       </c>
       <c r="B68" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>¿Son estos sueños reales?</t>
+          <t>¿Son solo sueños o metas reales?</t>
         </is>
       </c>
       <c r="G68" t="inlineStr"/>
@@ -2917,7 +2917,7 @@
         <v>32</v>
       </c>
       <c r="B69" t="n">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>En los pueblos donde todos pueden elegir, no hay una carrera pública como tal.</t>
+          <t>En los pueblos donde todos pueden elegir, no hay carrera pública.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr"/>
@@ -2953,7 +2953,7 @@
         <v>33</v>
       </c>
       <c r="B70" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sin entusiasmo, nunca se logra hacer algo grande.</t>
+          <t>Nunca se ha logrado algo grande sin entusiasmo.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr"/>
@@ -2989,7 +2989,7 @@
         <v>34</v>
       </c>
       <c r="B71" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Este método calcula interés sobre intereses.</t>
+          <t>Este método calcula intereses sobre intereses.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -3025,7 +3025,7 @@
         <v>35</v>
       </c>
       <c r="B72" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>El resultado es aproximadamente trescientos mil dólares en seis años.</t>
+          <t>El resultado es aproximadamente de $300,000 en seis años.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -3061,7 +3061,7 @@
         <v>36</v>
       </c>
       <c r="B73" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
